--- a/data/trans_dic/KIDMED_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,23; 74,39</t>
+          <t>49,67; 73,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,83; 71,34</t>
+          <t>59,48; 74,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,87; 69,69</t>
+          <t>57,43; 71,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,08; 74,01</t>
+          <t>64,33; 75,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,38; 74,39</t>
+          <t>65,46; 77,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,95; 72,88</t>
+          <t>66,49; 74,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,83; 56,54</t>
+          <t>43,26; 58,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,98; 58,85</t>
+          <t>46,21; 59,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 55,11</t>
+          <t>46,96; 57,9</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,91; 69,78</t>
+          <t>60,03; 72,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,03; 72,93</t>
+          <t>56,49; 69,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,5; 69,35</t>
+          <t>60,14; 69,26</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,51; 64,56</t>
+          <t>59,91; 67,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,54; 66,47</t>
+          <t>60,58; 66,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,0; 64,34</t>
+          <t>61,22; 66,18</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159924</t>
+          <t>159565</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68812; 84991</t>
+          <t>61039; 89955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62707; 97607</t>
+          <t>70539; 88571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135241; 174962</t>
+          <t>138693; 172158</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>188</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>163958</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>170934</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297791</t>
+          <t>292181</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>111818; 137742</t>
+          <t>148753; 175598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154410; 184135</t>
+          <t>118211; 139238</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>277319; 316011</t>
+          <t>273836; 307599</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85884</t>
+          <t>84763</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93457</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179342</t>
+          <t>166856</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52389; 106437</t>
+          <t>72034; 97109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80527; 107744</t>
+          <t>71648; 92601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136948; 204660</t>
+          <t>151018; 186180</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>148</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>104330</t>
+          <t>110722</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>118743</t>
+          <t>103337</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>214059</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93621; 114800</t>
+          <t>99750; 120854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106447; 129310</t>
+          <t>92638; 113510</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206819; 237053</t>
+          <t>198552; 228668</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>585</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>394014</t>
+          <t>439023</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>342979; 421661</t>
+          <t>411473; 463185</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>435981; 495052</t>
+          <t>374528; 412911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>796725; 899449</t>
+          <t>798965; 863679</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>64,75%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>67,44%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>49,67; 73,2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>59,48; 74,68</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57,43; 71,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>64,33; 75,94</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>65,46; 77,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>66,49; 74,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52,95%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>43,26; 58,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46,21; 59,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46,96; 57,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>66,63%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63,02%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>60,03; 72,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56,49; 69,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60,14; 69,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>63,67%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>59,91; 67,44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60,58; 66,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61,22; 66,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6475301174102701</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6744344868774493</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6607428492632821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>79579</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>79987</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>159565</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4966723873645632</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.594770364402667</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5743141572664211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>61039; 89955</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>70539; 88571</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>138693; 172158</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7319616377849932</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7468136132701502</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7128867089724747</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7090362579095932</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.710015539761053</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.709465682250757</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>163958</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>128224</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>292181</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.6432800605330361</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.6545727132462381</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6649198772403394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>148753; 175598</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>118211; 139238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>273836; 307599</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7593715955333489</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7710036968184788</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7469034169056784</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5090204486009139</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5294985367261149</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5188938335597296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>84763</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82092</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>166856</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4325770353600336</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4621290762406286</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.469640664262336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>72034; 97109</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>71648; 92601</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>151018; 186180</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5831590655264809</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5972770808542346</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5789908854693502</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6663404945783613</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6301831751788498</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6483815387087851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>110722</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>103337</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>214059</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.6003041817767421</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5649398991229365</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.6014110502862698</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>99750; 120854</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>92638; 113510</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>198552; 228668</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7273161259129522</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6922230432930633</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6926311402564453</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.639206958141206</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6367429309881053</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6380397214334881</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>439023</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>393640</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>832662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5990956357256126</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.6058277462766886</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.6122188019529697</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>411473; 463185</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>374528; 412911</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>798965; 863679</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.674386325971589</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6679161366000013</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6618076500263844</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>79579</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>79987</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>159565</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>61039</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>70539</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>138693</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>89955</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>88571</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>172158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>163958</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>128224</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>292181</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>148753</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>118211</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>273836</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>175598</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>139238</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>307599</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>84763</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>82092</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>166856</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>72034</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>71648</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>151018</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>97109</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>92601</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>186180</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>110722</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>103337</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>214059</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>99750</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>92638</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>198552</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>120854</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>113510</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>228668</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>613</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>585</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>439023</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>393640</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>832662</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>411473</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>374528</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>798965</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>463185</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>412911</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>863679</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>